--- a/src/订单/单子-姚足球-V3/result/lstm.xlsx
+++ b/src/订单/单子-姚足球-V3/result/lstm.xlsx
@@ -472,28 +472,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124.6403117889032</v>
+        <v>114.7049055695939</v>
       </c>
       <c r="B2" t="n">
-        <v>106.2994567564384</v>
+        <v>94.32988305786748</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6985047670128011</v>
+        <v>0.7446549873128139</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03058066075630906</v>
+        <v>0.02726680707714364</v>
       </c>
       <c r="E2" t="n">
-        <v>52.64279712203898</v>
+        <v>47.333631139791</v>
       </c>
       <c r="F2" t="n">
-        <v>41.63149487396354</v>
+        <v>37.2978139788994</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9896042252046953</v>
+        <v>0.991595370119403</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00928872748552727</v>
+        <v>0.008370802379686635</v>
       </c>
     </row>
   </sheetData>
